--- a/mpsoc/设计文档/addrmap&registers（待补充）.xlsx
+++ b/mpsoc/设计文档/addrmap&registers（待补充）.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -113,6 +113,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,319 +491,384 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" style="7" min="1" max="1"/>
+    <col width="17" customWidth="1" style="7" min="2" max="2"/>
+    <col width="21" customWidth="1" style="7" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>基地址</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>sys ctrl</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>0x40017000</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>系统控制寄存器</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>GPIO</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x40019000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>I2C</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x40021000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UART0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x40015000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UART1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x40026000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UART2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x40025000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WDT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x4001A000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Timer0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x40018000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Timer1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x40011000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>uC Slave</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>？？？？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>I2C</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SPI Master</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x40031000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SPI Slave</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>？？？？</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>UART0</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>UART1</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>UART2</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>WDT</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TIMOx3</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TIMIx3</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>uC Slave</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>SPI Master</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>SPI Slave</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>bootrom</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x60000000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SDRAM_cfg</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x54000000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SDRAM_MEM（64KB）</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x50000000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>SRAM（64KB）</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SDRAM（64KB）</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x60010000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Security/OTP</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>0x40012000</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>安全控制</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>DMACx8</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>QSPI</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0x42000000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QSPI0_cfg</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0x48000000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QSPI_MEM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x44000000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>PN-IRT</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x43c90000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>ESC0</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>0x44c80000</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>外部 EtherCAT 通信</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>GMAC</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>？？？？</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x40040000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>ESC1</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0x44c00000</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>背板 SYNC 同步</t>
         </is>
       </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IRAM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>（未填写）</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DRAM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>（未填写）</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -871,2041 +937,2041 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>寄存器名</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>关键位域</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>EtherCAT ESC 寄存器（Beckhoff ESC Section II），共 109 个</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" s="0" t="inlineStr"/>
+      <c r="C2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>ESC Information（0x0000–0x0009）</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" s="0" t="inlineStr"/>
+      <c r="C3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>0x0000</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>type[7:0]：EtherCAT 从站控制器类型（0x11=ET1100、0x12=ET1200、0x04=IP Core、0x02=ESC20）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>0x0001</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>revision[7:0]：版本号</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>0x0002</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>build[15:0]：构建号（IP Core：build[7:4]=次版本、build[3:0]=维护版本）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>0x0004</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>FMMUs supported</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>fmmu_count[7:0]：FMMU 数量（ET1100=8、ET1200=3、ESC20=4）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>0x0005</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>SyncManagers supported</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>sm_count[7:0]：SyncManager 数量（ET1100=8、ET1200=4、ESC20=4）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>0x0006</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>RAM Size</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>ram_size[7:0]：Process Data RAM 大小，单位 KB（ET1100=8、ET1200=1）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>0x0007</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Port Descriptor</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>port3[7:6]、port2[5:4]、port1[3:2]、port0[1:0]：各端口配置，编码 00=未实现/01=未配置（SII EEPROM 决定）/10=EBUS/11=MII/RMII/RGMII</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>ESC Features supported</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>fixed_fmmu_sm[11]：固定 FMMU/SM 配置；brw_aprw_fprw[10]：不支持 BRW/APRW/FPRW；lrw[9]：不支持 LRW；enh_dc_sync[8]：增强 DC SYNC 激活；sep_fcs[7]：独立 FCS 错误；enh_link_mii[6]：MII 增强链路检测；enh_link_ebus[5]：EBUS 增强链路检测；low_jitter_ebus[4]：EBUS 低抖动；dc_width[3]：DC 宽度（1=64 位）；dc[2]：分布式时钟可用；fmmu_op[0]：FMMU 操作（0=位映射/1=字节映射）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>Station Address（0x0010–0x0013）</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" s="0" t="inlineStr"/>
+      <c r="C12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>0x0010</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>Configured Station Address</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>addr[15:0]：配置站地址（节点寻址 FPxx 使用）（复位值 0x0000）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>0x0012</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Configured Station Alias</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>alias[15:0]：配置站别名（EEPROM 地址 0x0004 加载，DL Control[24] 使能后生效）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>Write Protection（0x0020–0x0031）</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" s="0" t="inlineStr"/>
+      <c r="C15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>0x0020</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Write Register Enable</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>enable[0]：写寄存器使能（写保护使能时须同帧先写本寄存器，值任意）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>0x0021</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Write Register Protection</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>protect[0]：写寄存器保护使能（保护 0x0000–0x0137 与 0x013A–0x0F0F，0x0030 除外）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>0x0030</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>ESC Write Enable</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>enable[0]：ESC 写使能（ESC 写保护使能时须同帧先写本寄存器）</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>0x0031</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>ESC Write Protection</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>protect[0]：ESC 写保护使能（保护所有区域，0x0030 除外）</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>Reset（0x0040–0x0041）</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" s="0" t="inlineStr"/>
+      <c r="C20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>0x0040</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>ESC Reset ECAT</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>reset[7:0]：连续 3 帧写 0x52('R')/0x45('E')/0x53('S') 触发 EtherCAT 核复位；progress[1:0]（读）：复位进度（01=已写 R、10=已写 RE、00=其它）</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>0x0041</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>ESC Reset PDI</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>reset[7:0]：同上序列复位 PDI；progress[1:0]（读）</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>Data Link Layer（0x0100–0x0111）</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="B23" s="0" t="inlineStr"/>
+      <c r="C23" s="0" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>0x0100</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>ESC DL Control</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>station_alias[24]：站别名使能（FPxx 用别名寻址）；ebus_remote_link_down[22]：EBUS 远程断链信号时间（0=~660ms/1=~80µs）；ebus_low_jitter[19]：EBUS 低抖动；rx_fifo_size[18:16]：RX FIFO 大小（0-7，复位 7）；loop_port3[15:14]、loop_port2[13:12]、loop_port1[11:10]、loop_port0[9:8]：各端口环回（00=Auto/01=Auto Close/10=Open/11=Closed）；temp_use[1]：临时环回（约 1 秒后恢复）；forwarding_rule[0]：转发规则（0=转发非 EtherCAT 帧/1=丢弃，复位 1）</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>0x0102</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>Extended ESC DL Control</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>（扩展数据链路控制，仅 IP Core）</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>0x0108</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>Physical Read/Write Offset</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>offset[15:0]：R/W 命令读/写地址偏移（RD_ADR=ADR、WR_ADR=ADR+Offset）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>0x0110</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>ESC DL Status</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>comm_port3[15]、loop_port3[14]、comm_port2[13]、loop_port2[12]、comm_port1[11]、loop_port1[10]、comm_port0[9]、loop_port0[8]：各端口通信建立/环回关闭；phy_link_port3[7]、phy_link_port2[6]、phy_link_port1[5]、phy_link_port0[4]：各端口物理链路（1=检测到 link）；enh_link[2]：增强链路检测；pdi_wd_status[1]：PDI 看门狗状态（0=超时/1=已重载）；pdi_operational[0]：PDI 运行/EEPROM 已加载（=1 是 Process RAM 可访问前提）</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>Application Layer（0x0120–0x0139）</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="B28" s="0" t="inlineStr"/>
+      <c r="C28" s="0" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>0x0120</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>AL Control</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>device_id[5]：设备识别请求；error_ind_ack[4]：Error Ind 应答；device_state[3:0]：请求状态（1=Init/2=Pre-Op/3=Bootstrap/4=Safe-Op/8=Operational）</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>0x0130</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>AL Status</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>device_id[5]：设备识别；error_ind[4]：设备未进入请求状态或因本地动作改变状态；actual_state[3:0]：实际状态（1=Init/2=Pre-Op/3=Bootstrap/4=Safe-Op/8=Operational）</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>0x0134</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>AL Status Code</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>code[15:0]：应用层状态码</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>0x0138</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>RUN LED Override</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>enable[4]：覆盖使能；led_code[3:0]：LED 编码（0x0=Off/0x1-0xC=闪 1-12 次/0xD=Blinking/0xE=Flickering/0xF=On）</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>0x0139</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>ERR LED Override</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>enable[4]：覆盖使能；led_code[3:0]：LED 编码（同 RUN）</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>PDI / ESC Configuration（0x0140–0x0153）</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+      <c r="B34" s="0" t="inlineStr"/>
+      <c r="C34" s="0" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>0x0140</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>PDI Control</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>pdi_type[7:0]：PDI 类型（0x00=无 PDI/0x04=Digital I/O/0x05=SPI Slave/0x06=Oversampling I/O/0x07=EtherCAT Bridge(端口3)/0x08=16 位异步 µC/0x09=8 位异步 µC/0x0A=16 位同步 µC/0x0B=8 位同步 µC/0x10-0x14=32DI~32DO/0x80=On-chip bus）</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>0x0141</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>ESC Configuration</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>enh_link_port3[7]、enh_link_port2[6]、enh_link_port1[5]、enh_link_port0[4]：各端口增强链路检测；dc_latch_in[3]：DC Latch In 单元；dc_sync_out[2]：DC SYNC Out 单元；enh_link_all[1]：所有端口增强链路检测（覆盖 [7:4]）；device_emulation[0]：设备仿真（0=AL status 由 PDI 设/1=自动取 AL control）</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>0x014E</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>PDI Information</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>pdi_config_invalid[3]：PDI 配置无效；pdi_active[2]：PDI 已激活；pdi_configured[1]：PDI 已配置；pdi_write_ack[0]：PDI 寄存器写应答使能</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>0x0150</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>PDI Configuration</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>依 PDI 类型：SPI 模式 spi_mode[1:0]/spi_irq_pol[3:2]/spi_sel_pol[4]/data_out_sample[5]；异步 µC busy_pol[1:0]/irq_pol[3:2]/bhe_pol[4]/rd_pol[7]；同步 µC ta_pol[1:0]/irq_pol[3:2]/bhe_pol[4]/adr0_pol[5]/byte_access[6]/ts_pol[7]；Digital I/O outvalid_pol[0]/outvalid_mode[1]/bidir[2]/wd_behaviour[3]/input_sample[5:4]/output_update[7:6]</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>0x0151</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>DC Sync/Latch Configuration</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>sync1_to_al_event[7]：SYNC1 映射到 AL Event 0x0220.3；sync1_latch1[6]：SYNC1/LATCH1 选择；sync1_pol[5:4]：SYNC1 驱动/极性；sync0_to_al_event[3]：SYNC0 映射到 0x0220.2；sync0_latch0[2]：SYNC0/LATCH0 选择；sync0_pol[1:0]：SYNC0 驱动/极性</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>0x0152</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>Extended PDI Configuration</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>Digital I/O：每对 I/O 方向 [15:0]；同步 µC：write_data_valid[8]/read_mode[9]/cs_sample[10]/ta_update[11]；异步 µC：read_busy_delay[0]/write_timing[1]；On-chip bus：read_prefetch[1:0]/axi_subtype[10:8]</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>Interrupts / Events（0x0200–0x0223）</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+      <c r="B41" s="0" t="inlineStr"/>
+      <c r="C41" s="0" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>0x0200</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>ECAT Event Mask</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>mask[15:0]：把 ECAT Event Request 位映射到帧的 ECAT event 字段（0=不映射/1=映射）</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>0x0204</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>PDI AL Event Mask</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>mask[15:0]：把 AL Event Request 映射到 PDI IRQ 信号（复位值 0x00FF）</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>0x0210</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>ECAT Event Request</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>sm_status_mirror[11:4]：SM0-7 状态镜像；al_status_event[3]：AL Status 事件（读 0x0130 清除）；dl_status_event[2]：DL Status 事件（读 0x0110 清除）；dc_latch_event[0]：DC Latch 事件（读 Latch 时间清除）</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>0x0220</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>AL Event Request</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>sm_int[23:8]：SM0-15 中断（SM Status[0]/[1]）；wd_process_data[6]：Process Data 看门狗（读 0x0440 清除）；eeprom_emulation[5]：EEPROM 仿真；sm_activation_changed[4]：SM 激活改变（读 0x0806 清除）；dc_sync1[3]：DC SYNC1 状态（读 0x098F 清除）；dc_sync0[2]：DC SYNC0 状态（读 0x098E 清除）；dc_latch_event[1]：DC Latch 事件；al_control_event[0]：AL Control 事件（PDI 读 0x0120 清除）</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>Error Counters（0x0300–0x0313）</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="B46" s="0" t="inlineStr"/>
+      <c r="C46" s="0" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>0x0300</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>RX Error Counter Port 0</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>rx_error[15:8]：RX 错误计数；invalid_frame[7:0]：无效帧计数（饱和 0xFF，写清除）</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>0x0302</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>RX Error Counter Port 1</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>rx_error[15:8]；invalid_frame[7:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>0x0304</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>RX Error Counter Port 2</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>rx_error[15:8]；invalid_frame[7:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>0x0306</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>RX Error Counter Port 3</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>rx_error[15:8]；invalid_frame[7:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>0x0308</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>Forwarded RX Error Port 0</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>fwd_rx_error[7:0]：转发 RX 错误计数（饱和 0xFF，写清除）</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>0x030A</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>Forwarded RX Error Port 1</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>fwd_rx_error[7:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>0x030C</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>ECAT Processing Unit Error Counter</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>ecu_error[7:0]：ECAT 处理单元帧错误计数</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>0x030D</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>PDI Error Counter</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>pdi_error[7:0]：PDI 错误计数</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
         <is>
           <t>0x030E</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>PDI Error Code</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>SPI：cmd[7:6]/写继续[5]/缺读终止[4]/读 busy 违例[3]/访问时钟周期数[2:0]；µC：写寻址错[3]/读寻址错[2]/写 busy 违例[1]/读 busy 违例[0]</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
         <is>
           <t>0x0310</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>Lost Link Counter Port 0</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>lost_link[7:0]：丢链计数（仅 Loop=Auto 时）</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="0" t="inlineStr">
         <is>
           <t>0x0312</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>Lost Link Counter Port 1</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>lost_link[7:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="0" t="inlineStr">
         <is>
           <t>Watchdogs（0x0400–0x0443）</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+      <c r="B58" s="0" t="inlineStr"/>
+      <c r="C58" s="0" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="0" t="inlineStr">
         <is>
           <t>0x0400</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>Watchdog Divider</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>wd_div[15:0]：看门狗分频器，25MHz tick 数减 2（复位值 0x09C2=2498→100µs）</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="0" t="inlineStr">
         <is>
           <t>0x0410</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>Watchdog Time PDI</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>wd_time_pdi[15:0]：PDI 看门狗时间（=0 禁用，复位值 0x03E8=100ms）</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="0" t="inlineStr">
         <is>
           <t>0x0420</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>Watchdog Time Process Data</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t>wd_time_pd[15:0]：过程数据看门狗时间（=0 禁用，复位值 0x03E8）</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="0" t="inlineStr">
         <is>
           <t>0x0440</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>Watchdog Status Process Data</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t>wd_status[0]：0=超时/1=激活或禁用</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="0" t="inlineStr">
         <is>
           <t>0x0442</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>Watchdog Counter Process Data</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="0" t="inlineStr">
         <is>
           <t>wd_counter[7:0]：过程数据看门狗超时计数（写 0x0442/0x0443 任一清两者）</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="0" t="inlineStr">
         <is>
           <t>0x0443</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>Watchdog Counter PDI</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
         <is>
           <t>wd_counter[7:0]：PDI 看门狗超时计数</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
         <is>
           <t>SII EEPROM Interface（0x0500–0x050F）</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
+      <c r="B65" s="0" t="inlineStr"/>
+      <c r="C65" s="0" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="0" t="inlineStr">
         <is>
           <t>0x0500</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>EEPROM Configuration</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>force_ecat[1]：强制 ECAT 访问（复位 0x0501.0）；pdi_ctrl[0]：EEPROM 控制权交给 PDI</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="0" t="inlineStr">
         <is>
           <t>0x0501</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>EEPROM PDI Access State</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>pdi_access[0]：=1 时 PDI 拥有 EEPROM 控制权</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="0" t="inlineStr">
         <is>
           <t>0x0502</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>EEPROM Control/Status</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="0" t="inlineStr">
         <is>
           <t>busy[15]：忙；err_write_enable[14]：无写使能的写；err_ack_cmd[13]：缺应答/无效命令；err_device_info[12]：EEPROM 加载失败；checksum_err[11]：ESC 配置区校验错；cmd[10:8]：命令（000=空闲/清错、001=读、010=写、100=重载）；eeprom_algorithm[7]：地址字节数（0=1 字节/1=2 字节）；eeprom_read_bytes[6]：读字节数（0=4/1=8，ET1100/ET1200=1）；emulation[5]：EEPROM 仿真；write_enable[0]：写请求使能</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="0" t="inlineStr">
         <is>
           <t>0x0504</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>EEPROM Address</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="0" t="inlineStr">
         <is>
           <t>addr[17:0]：EEPROM 地址（≤16Kbit 用 [9:0]、32Kbit–4Mbit 用 [17:0]、仿真用 [31:0]）</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="0" t="inlineStr">
         <is>
           <t>0x0508</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>EEPROM Data</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
         <is>
           <t>data[63:0]：EEPROM 数据（写 [15:0]、读 [63:16]）</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="0" t="inlineStr">
         <is>
           <t>MII Management（0x0510–0x051B）</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
+      <c r="B71" s="0" t="inlineStr"/>
+      <c r="C71" s="0" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="0" t="inlineStr">
         <is>
           <t>0x0510</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>MII Management Control/Status</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="0" t="inlineStr">
         <is>
           <t>busy[15]：忙；cmd_error[14]：命令错误；read_error[13]：读错误；cmd[9:8]：命令（00=空闲/清错、01=读、10=写）；port0_phy_addr[7:3]：Port0 PHY 地址；mi_link_detect[2]：MI 链路检测激活；pdi_ctrl[1]：MI 由 PDI 可控；write_enable[0]：写使能</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="0" t="inlineStr">
         <is>
           <t>0x0512</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>MII PHY Address</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="0" t="inlineStr">
         <is>
           <t>show_independent[7]：显示独立地址；phy_addr[4:0]：PHY 地址</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="0" t="inlineStr">
         <is>
           <t>0x0513</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>MII PHY Register Address</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="0" t="inlineStr">
         <is>
           <t>phy_reg[4:0]：PHY 寄存器号</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
         <is>
           <t>0x0514</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>MII PHY Data</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>data[15:0]：PHY 读/写数据</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="0" t="inlineStr">
         <is>
           <t>0x0516</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>MII ECAT Access State</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="0" t="inlineStr">
         <is>
           <t>ecat_access[0]：ECAT 请求独占</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="0" t="inlineStr">
         <is>
           <t>0x0517</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="0" t="inlineStr">
         <is>
           <t>MII PDI Access State</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="0" t="inlineStr">
         <is>
           <t>force_reset[1]：强制复位；pdi_access[0]：=1 时 PDI 拥有 MI 访问</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="0" t="inlineStr">
         <is>
           <t>0x0518</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>PHY Port Status（Port0–3）</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="0" t="inlineStr">
         <is>
           <t>每端口 1 字节：phy_config_updated[5]：PHY 配置已更新；peer_error[4]：对端错误；read_error[3]：读错误；link_error[2]：链路错误；link_full_duplex[1]：link（100M 全双工）；phy_link[0]：物理 link</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="0" t="inlineStr">
         <is>
           <t>FMMU（0x0600–0x06FF）</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
+      <c r="B79" s="0" t="inlineStr"/>
+      <c r="C79" s="0" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="0" t="inlineStr">
         <is>
           <t>0x0600</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>FMMU（8 通道 × 16 字节）</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="0" t="inlineStr">
         <is>
           <t>地址=0x0600+y×16+偏移。每通道：Logical Start Address[+0x0]：逻辑起始地址；Length[+0x4]：逻辑字节数；Logical Start bit[+0x6][2:0]：逻辑起始位；Logical Stop bit[+0x7][2:0]：逻辑结束位；Physical Start Address[+0x8]：物理起始地址；Physical Start bit[+0xA][2:0]：物理起始位；Type[+0xB]（bit0=读映射/bit1=写映射）；Activate[+0xC]（bit0=激活）</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="0" t="inlineStr">
         <is>
           <t>SyncManager（0x0800–0x087F）</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
+      <c r="B81" s="0" t="inlineStr"/>
+      <c r="C81" s="0" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="0" t="inlineStr">
         <is>
           <t>0x0800</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="0" t="inlineStr">
         <is>
           <t>SyncManager（8 通道 × 8 字节）</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="0" t="inlineStr">
         <is>
           <t>地址=0x0800+y×8+偏移。每通道：Physical Start Address[+0x0]；Length[+0x2]；Control[+0x4]（[1:0]模式 00=Buffered(3 缓冲)/10=Mailbox(单缓冲)；[3:2]方向 00=Read(ECAT 读/PDI 写)/01=Write(ECAT 写/PDI 读)；[4]ECAT 事件中断；[5]PDI 事件中断；[6]看门狗触发）；Status[+0x5]（[0]写中断/[1]读中断/[3]邮箱满/[5:4]最后写入缓冲/[6]读缓冲占用/[7]写缓冲占用）；Activate[+0x6]（[0]使能/[1]Repeat Request/[6]ECAT Latch/[7]PDI Latch）；PDI Control[+0x7]（[0]停用/[1]Repeat Ack）</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="0" t="inlineStr">
         <is>
           <t>Distributed Clocks（0x0900–0x09FF）</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
+      <c r="B83" s="0" t="inlineStr"/>
+      <c r="C83" s="0" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="0" t="inlineStr">
         <is>
           <t>0x0900</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="0" t="inlineStr">
         <is>
           <t>Receive Time Port 0</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：写=锁存各端口接收帧开始本地时间；读=最近一次含写访问帧开始时间</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="0" t="inlineStr">
         <is>
           <t>0x0904</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="0" t="inlineStr">
         <is>
           <t>Receive Time Port 1</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="0" t="inlineStr">
         <is>
           <t>0x0908</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="0" t="inlineStr">
         <is>
           <t>Receive Time Port 2</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="0" t="inlineStr">
         <is>
           <t>0x090C</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="0" t="inlineStr">
         <is>
           <t>Receive Time Port 3</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="0" t="inlineStr">
         <is>
           <t>0x0910</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="0" t="inlineStr">
         <is>
           <t>System Time</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：64 位本地系统时间（1ns 基准，2000-01-01 起）</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="0" t="inlineStr">
         <is>
           <t>0x0918</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="0" t="inlineStr">
         <is>
           <t>Receive Time EPU</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：ECAT 处理单元收到帧开始时间</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="0" t="inlineStr">
         <is>
           <t>0x0920</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="0" t="inlineStr">
         <is>
           <t>System Time Offset</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="0" t="inlineStr">
         <is>
           <t>offset[63:0]：本地时间与 System Time 之差（加到本地时间）</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="0" t="inlineStr">
         <is>
           <t>0x0928</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="0" t="inlineStr">
         <is>
           <t>System Time Delay</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="0" t="inlineStr">
         <is>
           <t>delay[31:0]：参考时钟与 ESC 间传播延迟</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="0" t="inlineStr">
         <is>
           <t>0x092C</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="0" t="inlineStr">
         <is>
           <t>System Time Difference</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="0" t="inlineStr">
         <is>
           <t>sign[31]：符号位；diff[30:0]：本地副本与收到 System Time 的平均差</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="0" t="inlineStr">
         <is>
           <t>0x0930</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="0" t="inlineStr">
         <is>
           <t>Speed Counter Start</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="0" t="inlineStr">
         <is>
           <t>start[15:0]：调整带宽（复位值 0x1000，范围 0x0080–0x3FFF）</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="0" t="inlineStr">
         <is>
           <t>0x0932</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="0" t="inlineStr">
         <is>
           <t>Speed Counter Diff</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="0" t="inlineStr">
         <is>
           <t>diff[15:0]：本地/参考时钟周期偏差（补码）</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="0" t="inlineStr">
         <is>
           <t>0x0934</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="0" t="inlineStr">
         <is>
           <t>System Time Difference Filter Depth</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="0" t="inlineStr">
         <is>
           <t>depth[7:0]：滤波深度（复位值 4）</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="0" t="inlineStr">
         <is>
           <t>0x0935</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="0" t="inlineStr">
         <is>
           <t>Speed Counter Filter Depth</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="0" t="inlineStr">
         <is>
           <t>depth[7:0]：滤波深度（复位值 12）</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="0" t="inlineStr">
         <is>
           <t>0x0936</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="0" t="inlineStr">
         <is>
           <t>Receive Time Latch Mode</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="0" t="inlineStr">
         <is>
           <t>mode[0]：0=转发/1=反向</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="0" t="inlineStr">
         <is>
           <t>0x0980</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="0" t="inlineStr">
         <is>
           <t>Cyclic Unit Control</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="0" t="inlineStr">
         <is>
           <t>latch1_ctrl[5]、latch0_ctrl[4]、sync_out_ctrl[0]：各单元控制（0=ECAT/1=PDI）</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="0" t="inlineStr">
         <is>
           <t>0x0981</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="0" t="inlineStr">
         <is>
           <t>DC Activation</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="0" t="inlineStr">
         <is>
           <t>debug_pulse[7]：调试脉冲；near_future[6]：Near future（0=½DC 宽度/1=~2.1s）；start_time_check[5]：开始时间合理性检查；start_time_64[4]：开始时间扩展 64 位；auto_activate[3]：写开始时间自动激活；sync1_gen[2]：SYNC1 产生；sync0_gen[1]：SYNC0 产生；sync_out_activate[0]：Sync Out 激活</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="0" t="inlineStr">
         <is>
           <t>0x0982</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="0" t="inlineStr">
         <is>
           <t>Pulse Length of SyncSignals</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="0" t="inlineStr">
         <is>
           <t>pulse_len[15:0]：SYNC 脉冲宽度（10ns 单位，0=Acknowledge 模式）</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="0" t="inlineStr">
         <is>
           <t>0x0984</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="0" t="inlineStr">
         <is>
           <t>DC Activation Status</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="0" t="inlineStr">
         <is>
           <t>start_time_check_result[2]：开始时间合理性结果；sync1_pending[1]：SYNC1 挂起；sync0_pending[0]：SYNC0 挂起</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="0" t="inlineStr">
         <is>
           <t>0x098E</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="0" t="inlineStr">
         <is>
           <t>SYNC0 Status</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="0" t="inlineStr">
         <is>
           <t>status[7:0]：Acknowledge 模式状态（读清除）</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="0" t="inlineStr">
         <is>
           <t>0x098F</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="0" t="inlineStr">
         <is>
           <t>SYNC1 Status</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="0" t="inlineStr">
         <is>
           <t>status[7:0]：Acknowledge 模式状态（读清除）</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="0" t="inlineStr">
         <is>
           <t>0x0990</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="0" t="inlineStr">
         <is>
           <t>Start Time Cyclic Operation / Next SYNC0 Pulse</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：写=循环开始时间（ns）；读=下一 SYNC0 脉冲时间</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="0" t="inlineStr">
         <is>
           <t>0x0998</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>Next SYNC1 Pulse</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：下一 SYNC1 脉冲时间</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="0" t="inlineStr">
         <is>
           <t>0x09A0</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="0" t="inlineStr">
         <is>
           <t>SYNC0 Cycle Time</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="0" t="inlineStr">
         <is>
           <t>cycle[31:0]：SYNC0 脉冲间隔（ns，0=单次模式）</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="0" t="inlineStr">
         <is>
           <t>0x09A4</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="0" t="inlineStr">
         <is>
           <t>SYNC1 Cycle Time</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="0" t="inlineStr">
         <is>
           <t>cycle[31:0]：SYNC1 相对 SYNC0 延时（ns，0=跟随 SYNC0）</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="0" t="inlineStr">
         <is>
           <t>0x09A8</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="0" t="inlineStr">
         <is>
           <t>Latch0 Control</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="0" t="inlineStr">
         <is>
           <t>neg_edge[1]：负沿；pos_edge[0]：正沿（0=连续/1=单事件）</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="0" t="inlineStr">
         <is>
           <t>0x09A9</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="0" t="inlineStr">
         <is>
           <t>Latch1 Control</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="0" t="inlineStr">
         <is>
           <t>neg_edge[1]；pos_edge[0]：同 Latch0</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="0" t="inlineStr">
         <is>
           <t>0x09AE</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="0" t="inlineStr">
         <is>
           <t>Latch0 Status</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="0" t="inlineStr">
         <is>
           <t>pin_state[2]：引脚状态；neg_edge_event[1]：负沿事件；pos_edge_event[0]：正沿事件</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="0" t="inlineStr">
         <is>
           <t>0x09AF</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="0" t="inlineStr">
         <is>
           <t>Latch1 Status</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="0" t="inlineStr">
         <is>
           <t>pin_state[2]；neg_edge_event[1]；pos_edge_event[0]：同 Latch0</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="0" t="inlineStr">
         <is>
           <t>0x09B0</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="0" t="inlineStr">
         <is>
           <t>Latch0 Positive Edge</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：Latch0 正沿时间</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="0" t="inlineStr">
         <is>
           <t>0x09B8</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="0" t="inlineStr">
         <is>
           <t>Latch0 Negative Edge</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：Latch0 负沿时间</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="0" t="inlineStr">
         <is>
           <t>0x09C0</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="0" t="inlineStr">
         <is>
           <t>Latch1 Positive Edge</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：Latch1 正沿时间</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="0" t="inlineStr">
         <is>
           <t>0x09C8</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="0" t="inlineStr">
         <is>
           <t>Latch1 Negative Edge</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：Latch1 负沿时间</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="0" t="inlineStr">
         <is>
           <t>0x09F0</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="0" t="inlineStr">
         <is>
           <t>EtherCAT Buffer Change Event Time</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：EtherCAT 缓冲改变事件时间</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="0" t="inlineStr">
         <is>
           <t>0x09F8</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="0" t="inlineStr">
         <is>
           <t>PDI Buffer Start Event Time</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：PDI 缓冲开始事件时间</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="0" t="inlineStr">
         <is>
           <t>0x09FC</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="0" t="inlineStr">
         <is>
           <t>PDI Buffer Change Event Time</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：PDI 缓冲改变事件时间</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="0" t="inlineStr">
         <is>
           <t>ESC specific（0x0E00–0x0EFF）</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
+      <c r="B119" s="0" t="inlineStr"/>
+      <c r="C119" s="0" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="0" t="inlineStr">
         <is>
           <t>0x0E00</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="0" t="inlineStr">
         <is>
           <t>Power-On Values</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="0" t="inlineStr">
         <is>
           <t>ET1100：linkpol[14]：PHY 链路极性；phyad_off[13]：PHY 地址偏移（1=+16）；ctrl_status_move[12]：控制/状态信号映射；trans_mode_ena[11]：透明模式 MII；c25_ena[10]：CLK25 输出使能；c25_shi[9:8]：CLK25 移位；clk_mode[7:6]：CPU 时钟输出；p_conf[5:2]：每端口 EBUS(0)/MII(1)；p_mode[1:0]：逻辑端口数（2/3/4）</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="0" t="inlineStr">
         <is>
           <t>0x0E00</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="0" t="inlineStr">
         <is>
           <t>Product ID（0x0E00:0x0E07）</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="0" t="inlineStr">
         <is>
           <t>department[31:24]：部门；company[23:0]：厂商（仅 IP Core）</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="0" t="inlineStr">
         <is>
           <t>0x0E08</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="0" t="inlineStr">
         <is>
           <t>Vendor ID（0x0E08:0x0E0F）</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="0" t="inlineStr">
         <is>
           <t>department[31:24]：部门；company[23:0]：厂商（仅 IP Core）</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="0" t="inlineStr">
         <is>
           <t>ESC specific I/O（0x0F00–0x0F1F）</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
+      <c r="B123" s="0" t="inlineStr"/>
+      <c r="C123" s="0" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="0" t="inlineStr">
         <is>
           <t>0x0F00</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="0" t="inlineStr">
         <is>
           <t>Digital I/O Output Data</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="0" t="inlineStr">
         <is>
           <t>output[31:0]：32 位数字输出（可按位写，用逻辑寻址）</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="0" t="inlineStr">
         <is>
           <t>0x0F10</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="0" t="inlineStr">
         <is>
           <t>General Purpose Outputs</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="0" t="inlineStr">
         <is>
           <t>gpo[15:0]：通用输出（宽度 1/2/4/8 字节依 PDI）</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="0" t="inlineStr">
         <is>
           <t>0x0F18</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="0" t="inlineStr">
         <is>
           <t>General Purpose Inputs</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="0" t="inlineStr">
         <is>
           <t>gpi[15:0]：通用输入</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="0" t="inlineStr">
         <is>
           <t>User RAM / Process Data RAM</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
+      <c r="B127" s="0" t="inlineStr"/>
+      <c r="C127" s="0" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="0" t="inlineStr">
         <is>
           <t>0x0F80</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="0" t="inlineStr">
         <is>
           <t>User RAM</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="0" t="inlineStr">
         <is>
           <t>ram[127:0]：用户 RAM（128 字节）</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="0" t="inlineStr">
         <is>
           <t>0x1000</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="0" t="inlineStr">
         <is>
           <t>Process Data RAM</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="0" t="inlineStr">
         <is>
           <t>ram[7:0]（×8KB）：过程数据 RAM（ET1100=8KB；仅在 EEPROM 正确加载后 0x0110[0]=1 可访问）</t>
         </is>
@@ -2926,2041 +2992,2041 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>寄存器名</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>关键位域</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>EtherCAT ESC 寄存器（Beckhoff ESC Section II），共 109 个</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" s="0" t="inlineStr"/>
+      <c r="C2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>ESC Information（0x0000–0x0009）</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" s="0" t="inlineStr"/>
+      <c r="C3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>0x0000</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>type[7:0]：EtherCAT 从站控制器类型（0x11=ET1100、0x12=ET1200、0x04=IP Core、0x02=ESC20）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>0x0001</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>revision[7:0]：版本号</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>0x0002</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>build[15:0]：构建号（IP Core：build[7:4]=次版本、build[3:0]=维护版本）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>0x0004</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>FMMUs supported</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>fmmu_count[7:0]：FMMU 数量（ET1100=8、ET1200=3、ESC20=4）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>0x0005</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>SyncManagers supported</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>sm_count[7:0]：SyncManager 数量（ET1100=8、ET1200=4、ESC20=4）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>0x0006</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>RAM Size</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>ram_size[7:0]：Process Data RAM 大小，单位 KB（ET1100=8、ET1200=1）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>0x0007</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Port Descriptor</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>port3[7:6]、port2[5:4]、port1[3:2]、port0[1:0]：各端口配置，编码 00=未实现/01=未配置（SII EEPROM 决定）/10=EBUS/11=MII/RMII/RGMII</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>ESC Features supported</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>fixed_fmmu_sm[11]：固定 FMMU/SM 配置；brw_aprw_fprw[10]：不支持 BRW/APRW/FPRW；lrw[9]：不支持 LRW；enh_dc_sync[8]：增强 DC SYNC 激活；sep_fcs[7]：独立 FCS 错误；enh_link_mii[6]：MII 增强链路检测；enh_link_ebus[5]：EBUS 增强链路检测；low_jitter_ebus[4]：EBUS 低抖动；dc_width[3]：DC 宽度（1=64 位）；dc[2]：分布式时钟可用；fmmu_op[0]：FMMU 操作（0=位映射/1=字节映射）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>Station Address（0x0010–0x0013）</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" s="0" t="inlineStr"/>
+      <c r="C12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>0x0010</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>Configured Station Address</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>addr[15:0]：配置站地址（节点寻址 FPxx 使用）（复位值 0x0000）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>0x0012</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Configured Station Alias</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>alias[15:0]：配置站别名（EEPROM 地址 0x0004 加载，DL Control[24] 使能后生效）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>Write Protection（0x0020–0x0031）</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" s="0" t="inlineStr"/>
+      <c r="C15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>0x0020</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Write Register Enable</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>enable[0]：写寄存器使能（写保护使能时须同帧先写本寄存器，值任意）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>0x0021</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Write Register Protection</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>protect[0]：写寄存器保护使能（保护 0x0000–0x0137 与 0x013A–0x0F0F，0x0030 除外）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>0x0030</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>ESC Write Enable</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>enable[0]：ESC 写使能（ESC 写保护使能时须同帧先写本寄存器）</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>0x0031</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>ESC Write Protection</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>protect[0]：ESC 写保护使能（保护所有区域，0x0030 除外）</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>Reset（0x0040–0x0041）</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" s="0" t="inlineStr"/>
+      <c r="C20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>0x0040</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>ESC Reset ECAT</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>reset[7:0]：连续 3 帧写 0x52('R')/0x45('E')/0x53('S') 触发 EtherCAT 核复位；progress[1:0]（读）：复位进度（01=已写 R、10=已写 RE、00=其它）</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>0x0041</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>ESC Reset PDI</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>reset[7:0]：同上序列复位 PDI；progress[1:0]（读）</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>Data Link Layer（0x0100–0x0111）</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="B23" s="0" t="inlineStr"/>
+      <c r="C23" s="0" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>0x0100</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>ESC DL Control</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>station_alias[24]：站别名使能（FPxx 用别名寻址）；ebus_remote_link_down[22]：EBUS 远程断链信号时间（0=~660ms/1=~80µs）；ebus_low_jitter[19]：EBUS 低抖动；rx_fifo_size[18:16]：RX FIFO 大小（0-7，复位 7）；loop_port3[15:14]、loop_port2[13:12]、loop_port1[11:10]、loop_port0[9:8]：各端口环回（00=Auto/01=Auto Close/10=Open/11=Closed）；temp_use[1]：临时环回（约 1 秒后恢复）；forwarding_rule[0]：转发规则（0=转发非 EtherCAT 帧/1=丢弃，复位 1）</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>0x0102</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>Extended ESC DL Control</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>（扩展数据链路控制，仅 IP Core）</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>0x0108</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>Physical Read/Write Offset</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>offset[15:0]：R/W 命令读/写地址偏移（RD_ADR=ADR、WR_ADR=ADR+Offset）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>0x0110</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>ESC DL Status</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>comm_port3[15]、loop_port3[14]、comm_port2[13]、loop_port2[12]、comm_port1[11]、loop_port1[10]、comm_port0[9]、loop_port0[8]：各端口通信建立/环回关闭；phy_link_port3[7]、phy_link_port2[6]、phy_link_port1[5]、phy_link_port0[4]：各端口物理链路（1=检测到 link）；enh_link[2]：增强链路检测；pdi_wd_status[1]：PDI 看门狗状态（0=超时/1=已重载）；pdi_operational[0]：PDI 运行/EEPROM 已加载（=1 是 Process RAM 可访问前提）</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>Application Layer（0x0120–0x0139）</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="B28" s="0" t="inlineStr"/>
+      <c r="C28" s="0" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>0x0120</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>AL Control</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>device_id[5]：设备识别请求；error_ind_ack[4]：Error Ind 应答；device_state[3:0]：请求状态（1=Init/2=Pre-Op/3=Bootstrap/4=Safe-Op/8=Operational）</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>0x0130</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>AL Status</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>device_id[5]：设备识别；error_ind[4]：设备未进入请求状态或因本地动作改变状态；actual_state[3:0]：实际状态（1=Init/2=Pre-Op/3=Bootstrap/4=Safe-Op/8=Operational）</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>0x0134</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>AL Status Code</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>code[15:0]：应用层状态码</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>0x0138</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>RUN LED Override</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>enable[4]：覆盖使能；led_code[3:0]：LED 编码（0x0=Off/0x1-0xC=闪 1-12 次/0xD=Blinking/0xE=Flickering/0xF=On）</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>0x0139</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>ERR LED Override</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>enable[4]：覆盖使能；led_code[3:0]：LED 编码（同 RUN）</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>PDI / ESC Configuration（0x0140–0x0153）</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+      <c r="B34" s="0" t="inlineStr"/>
+      <c r="C34" s="0" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>0x0140</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>PDI Control</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>pdi_type[7:0]：PDI 类型（0x00=无 PDI/0x04=Digital I/O/0x05=SPI Slave/0x06=Oversampling I/O/0x07=EtherCAT Bridge(端口3)/0x08=16 位异步 µC/0x09=8 位异步 µC/0x0A=16 位同步 µC/0x0B=8 位同步 µC/0x10-0x14=32DI~32DO/0x80=On-chip bus）</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>0x0141</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>ESC Configuration</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>enh_link_port3[7]、enh_link_port2[6]、enh_link_port1[5]、enh_link_port0[4]：各端口增强链路检测；dc_latch_in[3]：DC Latch In 单元；dc_sync_out[2]：DC SYNC Out 单元；enh_link_all[1]：所有端口增强链路检测（覆盖 [7:4]）；device_emulation[0]：设备仿真（0=AL status 由 PDI 设/1=自动取 AL control）</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>0x014E</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>PDI Information</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>pdi_config_invalid[3]：PDI 配置无效；pdi_active[2]：PDI 已激活；pdi_configured[1]：PDI 已配置；pdi_write_ack[0]：PDI 寄存器写应答使能</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>0x0150</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>PDI Configuration</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>依 PDI 类型：SPI 模式 spi_mode[1:0]/spi_irq_pol[3:2]/spi_sel_pol[4]/data_out_sample[5]；异步 µC busy_pol[1:0]/irq_pol[3:2]/bhe_pol[4]/rd_pol[7]；同步 µC ta_pol[1:0]/irq_pol[3:2]/bhe_pol[4]/adr0_pol[5]/byte_access[6]/ts_pol[7]；Digital I/O outvalid_pol[0]/outvalid_mode[1]/bidir[2]/wd_behaviour[3]/input_sample[5:4]/output_update[7:6]</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>0x0151</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>DC Sync/Latch Configuration</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>sync1_to_al_event[7]：SYNC1 映射到 AL Event 0x0220.3；sync1_latch1[6]：SYNC1/LATCH1 选择；sync1_pol[5:4]：SYNC1 驱动/极性；sync0_to_al_event[3]：SYNC0 映射到 0x0220.2；sync0_latch0[2]：SYNC0/LATCH0 选择；sync0_pol[1:0]：SYNC0 驱动/极性</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>0x0152</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>Extended PDI Configuration</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>Digital I/O：每对 I/O 方向 [15:0]；同步 µC：write_data_valid[8]/read_mode[9]/cs_sample[10]/ta_update[11]；异步 µC：read_busy_delay[0]/write_timing[1]；On-chip bus：read_prefetch[1:0]/axi_subtype[10:8]</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>Interrupts / Events（0x0200–0x0223）</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+      <c r="B41" s="0" t="inlineStr"/>
+      <c r="C41" s="0" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>0x0200</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>ECAT Event Mask</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>mask[15:0]：把 ECAT Event Request 位映射到帧的 ECAT event 字段（0=不映射/1=映射）</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>0x0204</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>PDI AL Event Mask</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>mask[15:0]：把 AL Event Request 映射到 PDI IRQ 信号（复位值 0x00FF）</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>0x0210</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>ECAT Event Request</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>sm_status_mirror[11:4]：SM0-7 状态镜像；al_status_event[3]：AL Status 事件（读 0x0130 清除）；dl_status_event[2]：DL Status 事件（读 0x0110 清除）；dc_latch_event[0]：DC Latch 事件（读 Latch 时间清除）</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>0x0220</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>AL Event Request</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>sm_int[23:8]：SM0-15 中断（SM Status[0]/[1]）；wd_process_data[6]：Process Data 看门狗（读 0x0440 清除）；eeprom_emulation[5]：EEPROM 仿真；sm_activation_changed[4]：SM 激活改变（读 0x0806 清除）；dc_sync1[3]：DC SYNC1 状态（读 0x098F 清除）；dc_sync0[2]：DC SYNC0 状态（读 0x098E 清除）；dc_latch_event[1]：DC Latch 事件；al_control_event[0]：AL Control 事件（PDI 读 0x0120 清除）</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>Error Counters（0x0300–0x0313）</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="B46" s="0" t="inlineStr"/>
+      <c r="C46" s="0" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>0x0300</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>RX Error Counter Port 0</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>rx_error[15:8]：RX 错误计数；invalid_frame[7:0]：无效帧计数（饱和 0xFF，写清除）</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>0x0302</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>RX Error Counter Port 1</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>rx_error[15:8]；invalid_frame[7:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>0x0304</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>RX Error Counter Port 2</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>rx_error[15:8]；invalid_frame[7:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>0x0306</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>RX Error Counter Port 3</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>rx_error[15:8]；invalid_frame[7:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>0x0308</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>Forwarded RX Error Port 0</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>fwd_rx_error[7:0]：转发 RX 错误计数（饱和 0xFF，写清除）</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>0x030A</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>Forwarded RX Error Port 1</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>fwd_rx_error[7:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>0x030C</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>ECAT Processing Unit Error Counter</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>ecu_error[7:0]：ECAT 处理单元帧错误计数</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>0x030D</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>PDI Error Counter</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>pdi_error[7:0]：PDI 错误计数</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
         <is>
           <t>0x030E</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>PDI Error Code</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>SPI：cmd[7:6]/写继续[5]/缺读终止[4]/读 busy 违例[3]/访问时钟周期数[2:0]；µC：写寻址错[3]/读寻址错[2]/写 busy 违例[1]/读 busy 违例[0]</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
         <is>
           <t>0x0310</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>Lost Link Counter Port 0</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>lost_link[7:0]：丢链计数（仅 Loop=Auto 时）</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="0" t="inlineStr">
         <is>
           <t>0x0312</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>Lost Link Counter Port 1</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>lost_link[7:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="0" t="inlineStr">
         <is>
           <t>Watchdogs（0x0400–0x0443）</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+      <c r="B58" s="0" t="inlineStr"/>
+      <c r="C58" s="0" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="0" t="inlineStr">
         <is>
           <t>0x0400</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>Watchdog Divider</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>wd_div[15:0]：看门狗分频器，25MHz tick 数减 2（复位值 0x09C2=2498→100µs）</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="0" t="inlineStr">
         <is>
           <t>0x0410</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>Watchdog Time PDI</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>wd_time_pdi[15:0]：PDI 看门狗时间（=0 禁用，复位值 0x03E8=100ms）</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="0" t="inlineStr">
         <is>
           <t>0x0420</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>Watchdog Time Process Data</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t>wd_time_pd[15:0]：过程数据看门狗时间（=0 禁用，复位值 0x03E8）</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="0" t="inlineStr">
         <is>
           <t>0x0440</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>Watchdog Status Process Data</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t>wd_status[0]：0=超时/1=激活或禁用</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="0" t="inlineStr">
         <is>
           <t>0x0442</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>Watchdog Counter Process Data</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="0" t="inlineStr">
         <is>
           <t>wd_counter[7:0]：过程数据看门狗超时计数（写 0x0442/0x0443 任一清两者）</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="0" t="inlineStr">
         <is>
           <t>0x0443</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>Watchdog Counter PDI</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
         <is>
           <t>wd_counter[7:0]：PDI 看门狗超时计数</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
         <is>
           <t>SII EEPROM Interface（0x0500–0x050F）</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
+      <c r="B65" s="0" t="inlineStr"/>
+      <c r="C65" s="0" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="0" t="inlineStr">
         <is>
           <t>0x0500</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>EEPROM Configuration</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>force_ecat[1]：强制 ECAT 访问（复位 0x0501.0）；pdi_ctrl[0]：EEPROM 控制权交给 PDI</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="0" t="inlineStr">
         <is>
           <t>0x0501</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>EEPROM PDI Access State</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>pdi_access[0]：=1 时 PDI 拥有 EEPROM 控制权</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="0" t="inlineStr">
         <is>
           <t>0x0502</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>EEPROM Control/Status</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="0" t="inlineStr">
         <is>
           <t>busy[15]：忙；err_write_enable[14]：无写使能的写；err_ack_cmd[13]：缺应答/无效命令；err_device_info[12]：EEPROM 加载失败；checksum_err[11]：ESC 配置区校验错；cmd[10:8]：命令（000=空闲/清错、001=读、010=写、100=重载）；eeprom_algorithm[7]：地址字节数（0=1 字节/1=2 字节）；eeprom_read_bytes[6]：读字节数（0=4/1=8，ET1100/ET1200=1）；emulation[5]：EEPROM 仿真；write_enable[0]：写请求使能</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="0" t="inlineStr">
         <is>
           <t>0x0504</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>EEPROM Address</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="0" t="inlineStr">
         <is>
           <t>addr[17:0]：EEPROM 地址（≤16Kbit 用 [9:0]、32Kbit–4Mbit 用 [17:0]、仿真用 [31:0]）</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="0" t="inlineStr">
         <is>
           <t>0x0508</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>EEPROM Data</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
         <is>
           <t>data[63:0]：EEPROM 数据（写 [15:0]、读 [63:16]）</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="0" t="inlineStr">
         <is>
           <t>MII Management（0x0510–0x051B）</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
+      <c r="B71" s="0" t="inlineStr"/>
+      <c r="C71" s="0" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="0" t="inlineStr">
         <is>
           <t>0x0510</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>MII Management Control/Status</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="0" t="inlineStr">
         <is>
           <t>busy[15]：忙；cmd_error[14]：命令错误；read_error[13]：读错误；cmd[9:8]：命令（00=空闲/清错、01=读、10=写）；port0_phy_addr[7:3]：Port0 PHY 地址；mi_link_detect[2]：MI 链路检测激活；pdi_ctrl[1]：MI 由 PDI 可控；write_enable[0]：写使能</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="0" t="inlineStr">
         <is>
           <t>0x0512</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>MII PHY Address</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="0" t="inlineStr">
         <is>
           <t>show_independent[7]：显示独立地址；phy_addr[4:0]：PHY 地址</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="0" t="inlineStr">
         <is>
           <t>0x0513</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>MII PHY Register Address</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="0" t="inlineStr">
         <is>
           <t>phy_reg[4:0]：PHY 寄存器号</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
         <is>
           <t>0x0514</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>MII PHY Data</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>data[15:0]：PHY 读/写数据</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="0" t="inlineStr">
         <is>
           <t>0x0516</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>MII ECAT Access State</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="0" t="inlineStr">
         <is>
           <t>ecat_access[0]：ECAT 请求独占</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="0" t="inlineStr">
         <is>
           <t>0x0517</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="0" t="inlineStr">
         <is>
           <t>MII PDI Access State</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="0" t="inlineStr">
         <is>
           <t>force_reset[1]：强制复位；pdi_access[0]：=1 时 PDI 拥有 MI 访问</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="0" t="inlineStr">
         <is>
           <t>0x0518</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>PHY Port Status（Port0–3）</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="0" t="inlineStr">
         <is>
           <t>每端口 1 字节：phy_config_updated[5]：PHY 配置已更新；peer_error[4]：对端错误；read_error[3]：读错误；link_error[2]：链路错误；link_full_duplex[1]：link（100M 全双工）；phy_link[0]：物理 link</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="0" t="inlineStr">
         <is>
           <t>FMMU（0x0600–0x06FF）</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
+      <c r="B79" s="0" t="inlineStr"/>
+      <c r="C79" s="0" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="0" t="inlineStr">
         <is>
           <t>0x0600</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>FMMU（8 通道 × 16 字节）</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="0" t="inlineStr">
         <is>
           <t>地址=0x0600+y×16+偏移。每通道：Logical Start Address[+0x0]：逻辑起始地址；Length[+0x4]：逻辑字节数；Logical Start bit[+0x6][2:0]：逻辑起始位；Logical Stop bit[+0x7][2:0]：逻辑结束位；Physical Start Address[+0x8]：物理起始地址；Physical Start bit[+0xA][2:0]：物理起始位；Type[+0xB]（bit0=读映射/bit1=写映射）；Activate[+0xC]（bit0=激活）</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="0" t="inlineStr">
         <is>
           <t>SyncManager（0x0800–0x087F）</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
+      <c r="B81" s="0" t="inlineStr"/>
+      <c r="C81" s="0" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="0" t="inlineStr">
         <is>
           <t>0x0800</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="0" t="inlineStr">
         <is>
           <t>SyncManager（8 通道 × 8 字节）</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="0" t="inlineStr">
         <is>
           <t>地址=0x0800+y×8+偏移。每通道：Physical Start Address[+0x0]；Length[+0x2]；Control[+0x4]（[1:0]模式 00=Buffered(3 缓冲)/10=Mailbox(单缓冲)；[3:2]方向 00=Read(ECAT 读/PDI 写)/01=Write(ECAT 写/PDI 读)；[4]ECAT 事件中断；[5]PDI 事件中断；[6]看门狗触发）；Status[+0x5]（[0]写中断/[1]读中断/[3]邮箱满/[5:4]最后写入缓冲/[6]读缓冲占用/[7]写缓冲占用）；Activate[+0x6]（[0]使能/[1]Repeat Request/[6]ECAT Latch/[7]PDI Latch）；PDI Control[+0x7]（[0]停用/[1]Repeat Ack）</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="0" t="inlineStr">
         <is>
           <t>Distributed Clocks（0x0900–0x09FF）</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
+      <c r="B83" s="0" t="inlineStr"/>
+      <c r="C83" s="0" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="0" t="inlineStr">
         <is>
           <t>0x0900</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="0" t="inlineStr">
         <is>
           <t>Receive Time Port 0</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：写=锁存各端口接收帧开始本地时间；读=最近一次含写访问帧开始时间</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="0" t="inlineStr">
         <is>
           <t>0x0904</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="0" t="inlineStr">
         <is>
           <t>Receive Time Port 1</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="0" t="inlineStr">
         <is>
           <t>0x0908</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="0" t="inlineStr">
         <is>
           <t>Receive Time Port 2</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="0" t="inlineStr">
         <is>
           <t>0x090C</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="0" t="inlineStr">
         <is>
           <t>Receive Time Port 3</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：同 Port0</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="0" t="inlineStr">
         <is>
           <t>0x0910</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="0" t="inlineStr">
         <is>
           <t>System Time</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：64 位本地系统时间（1ns 基准，2000-01-01 起）</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="0" t="inlineStr">
         <is>
           <t>0x0918</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="0" t="inlineStr">
         <is>
           <t>Receive Time EPU</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：ECAT 处理单元收到帧开始时间</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="0" t="inlineStr">
         <is>
           <t>0x0920</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="0" t="inlineStr">
         <is>
           <t>System Time Offset</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="0" t="inlineStr">
         <is>
           <t>offset[63:0]：本地时间与 System Time 之差（加到本地时间）</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="0" t="inlineStr">
         <is>
           <t>0x0928</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="0" t="inlineStr">
         <is>
           <t>System Time Delay</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="0" t="inlineStr">
         <is>
           <t>delay[31:0]：参考时钟与 ESC 间传播延迟</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="0" t="inlineStr">
         <is>
           <t>0x092C</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="0" t="inlineStr">
         <is>
           <t>System Time Difference</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="0" t="inlineStr">
         <is>
           <t>sign[31]：符号位；diff[30:0]：本地副本与收到 System Time 的平均差</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="0" t="inlineStr">
         <is>
           <t>0x0930</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="0" t="inlineStr">
         <is>
           <t>Speed Counter Start</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="0" t="inlineStr">
         <is>
           <t>start[15:0]：调整带宽（复位值 0x1000，范围 0x0080–0x3FFF）</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="0" t="inlineStr">
         <is>
           <t>0x0932</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="0" t="inlineStr">
         <is>
           <t>Speed Counter Diff</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="0" t="inlineStr">
         <is>
           <t>diff[15:0]：本地/参考时钟周期偏差（补码）</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="0" t="inlineStr">
         <is>
           <t>0x0934</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="0" t="inlineStr">
         <is>
           <t>System Time Difference Filter Depth</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="0" t="inlineStr">
         <is>
           <t>depth[7:0]：滤波深度（复位值 4）</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="0" t="inlineStr">
         <is>
           <t>0x0935</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="0" t="inlineStr">
         <is>
           <t>Speed Counter Filter Depth</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="0" t="inlineStr">
         <is>
           <t>depth[7:0]：滤波深度（复位值 12）</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="0" t="inlineStr">
         <is>
           <t>0x0936</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="0" t="inlineStr">
         <is>
           <t>Receive Time Latch Mode</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="0" t="inlineStr">
         <is>
           <t>mode[0]：0=转发/1=反向</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="0" t="inlineStr">
         <is>
           <t>0x0980</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="0" t="inlineStr">
         <is>
           <t>Cyclic Unit Control</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="0" t="inlineStr">
         <is>
           <t>latch1_ctrl[5]、latch0_ctrl[4]、sync_out_ctrl[0]：各单元控制（0=ECAT/1=PDI）</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="0" t="inlineStr">
         <is>
           <t>0x0981</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="0" t="inlineStr">
         <is>
           <t>DC Activation</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="0" t="inlineStr">
         <is>
           <t>debug_pulse[7]：调试脉冲；near_future[6]：Near future（0=½DC 宽度/1=~2.1s）；start_time_check[5]：开始时间合理性检查；start_time_64[4]：开始时间扩展 64 位；auto_activate[3]：写开始时间自动激活；sync1_gen[2]：SYNC1 产生；sync0_gen[1]：SYNC0 产生；sync_out_activate[0]：Sync Out 激活</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="0" t="inlineStr">
         <is>
           <t>0x0982</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="0" t="inlineStr">
         <is>
           <t>Pulse Length of SyncSignals</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="0" t="inlineStr">
         <is>
           <t>pulse_len[15:0]：SYNC 脉冲宽度（10ns 单位，0=Acknowledge 模式）</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="0" t="inlineStr">
         <is>
           <t>0x0984</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="0" t="inlineStr">
         <is>
           <t>DC Activation Status</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="0" t="inlineStr">
         <is>
           <t>start_time_check_result[2]：开始时间合理性结果；sync1_pending[1]：SYNC1 挂起；sync0_pending[0]：SYNC0 挂起</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="0" t="inlineStr">
         <is>
           <t>0x098E</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="0" t="inlineStr">
         <is>
           <t>SYNC0 Status</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="0" t="inlineStr">
         <is>
           <t>status[7:0]：Acknowledge 模式状态（读清除）</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="0" t="inlineStr">
         <is>
           <t>0x098F</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="0" t="inlineStr">
         <is>
           <t>SYNC1 Status</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="0" t="inlineStr">
         <is>
           <t>status[7:0]：Acknowledge 模式状态（读清除）</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="0" t="inlineStr">
         <is>
           <t>0x0990</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="0" t="inlineStr">
         <is>
           <t>Start Time Cyclic Operation / Next SYNC0 Pulse</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：写=循环开始时间（ns）；读=下一 SYNC0 脉冲时间</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="0" t="inlineStr">
         <is>
           <t>0x0998</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>Next SYNC1 Pulse</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：下一 SYNC1 脉冲时间</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="0" t="inlineStr">
         <is>
           <t>0x09A0</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="0" t="inlineStr">
         <is>
           <t>SYNC0 Cycle Time</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="0" t="inlineStr">
         <is>
           <t>cycle[31:0]：SYNC0 脉冲间隔（ns，0=单次模式）</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="0" t="inlineStr">
         <is>
           <t>0x09A4</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="0" t="inlineStr">
         <is>
           <t>SYNC1 Cycle Time</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="0" t="inlineStr">
         <is>
           <t>cycle[31:0]：SYNC1 相对 SYNC0 延时（ns，0=跟随 SYNC0）</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="0" t="inlineStr">
         <is>
           <t>0x09A8</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="0" t="inlineStr">
         <is>
           <t>Latch0 Control</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="0" t="inlineStr">
         <is>
           <t>neg_edge[1]：负沿；pos_edge[0]：正沿（0=连续/1=单事件）</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="0" t="inlineStr">
         <is>
           <t>0x09A9</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="0" t="inlineStr">
         <is>
           <t>Latch1 Control</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="0" t="inlineStr">
         <is>
           <t>neg_edge[1]；pos_edge[0]：同 Latch0</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="0" t="inlineStr">
         <is>
           <t>0x09AE</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="0" t="inlineStr">
         <is>
           <t>Latch0 Status</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="0" t="inlineStr">
         <is>
           <t>pin_state[2]：引脚状态；neg_edge_event[1]：负沿事件；pos_edge_event[0]：正沿事件</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="0" t="inlineStr">
         <is>
           <t>0x09AF</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="0" t="inlineStr">
         <is>
           <t>Latch1 Status</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="0" t="inlineStr">
         <is>
           <t>pin_state[2]；neg_edge_event[1]；pos_edge_event[0]：同 Latch0</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="0" t="inlineStr">
         <is>
           <t>0x09B0</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="0" t="inlineStr">
         <is>
           <t>Latch0 Positive Edge</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：Latch0 正沿时间</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="0" t="inlineStr">
         <is>
           <t>0x09B8</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="0" t="inlineStr">
         <is>
           <t>Latch0 Negative Edge</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：Latch0 负沿时间</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="0" t="inlineStr">
         <is>
           <t>0x09C0</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="0" t="inlineStr">
         <is>
           <t>Latch1 Positive Edge</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：Latch1 正沿时间</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="0" t="inlineStr">
         <is>
           <t>0x09C8</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="0" t="inlineStr">
         <is>
           <t>Latch1 Negative Edge</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="0" t="inlineStr">
         <is>
           <t>time[63:0]：Latch1 负沿时间</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="0" t="inlineStr">
         <is>
           <t>0x09F0</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="0" t="inlineStr">
         <is>
           <t>EtherCAT Buffer Change Event Time</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：EtherCAT 缓冲改变事件时间</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="0" t="inlineStr">
         <is>
           <t>0x09F8</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="0" t="inlineStr">
         <is>
           <t>PDI Buffer Start Event Time</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：PDI 缓冲开始事件时间</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="0" t="inlineStr">
         <is>
           <t>0x09FC</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="0" t="inlineStr">
         <is>
           <t>PDI Buffer Change Event Time</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="0" t="inlineStr">
         <is>
           <t>time[31:0]：PDI 缓冲改变事件时间</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="0" t="inlineStr">
         <is>
           <t>ESC specific（0x0E00–0x0EFF）</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
+      <c r="B119" s="0" t="inlineStr"/>
+      <c r="C119" s="0" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="0" t="inlineStr">
         <is>
           <t>0x0E00</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="0" t="inlineStr">
         <is>
           <t>Power-On Values</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="0" t="inlineStr">
         <is>
           <t>ET1100：linkpol[14]：PHY 链路极性；phyad_off[13]：PHY 地址偏移（1=+16）；ctrl_status_move[12]：控制/状态信号映射；trans_mode_ena[11]：透明模式 MII；c25_ena[10]：CLK25 输出使能；c25_shi[9:8]：CLK25 移位；clk_mode[7:6]：CPU 时钟输出；p_conf[5:2]：每端口 EBUS(0)/MII(1)；p_mode[1:0]：逻辑端口数（2/3/4）</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="0" t="inlineStr">
         <is>
           <t>0x0E00</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="0" t="inlineStr">
         <is>
           <t>Product ID（0x0E00:0x0E07）</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="0" t="inlineStr">
         <is>
           <t>department[31:24]：部门；company[23:0]：厂商（仅 IP Core）</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="0" t="inlineStr">
         <is>
           <t>0x0E08</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="0" t="inlineStr">
         <is>
           <t>Vendor ID（0x0E08:0x0E0F）</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="0" t="inlineStr">
         <is>
           <t>department[31:24]：部门；company[23:0]：厂商（仅 IP Core）</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="0" t="inlineStr">
         <is>
           <t>ESC specific I/O（0x0F00–0x0F1F）</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
+      <c r="B123" s="0" t="inlineStr"/>
+      <c r="C123" s="0" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="0" t="inlineStr">
         <is>
           <t>0x0F00</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="0" t="inlineStr">
         <is>
           <t>Digital I/O Output Data</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="0" t="inlineStr">
         <is>
           <t>output[31:0]：32 位数字输出（可按位写，用逻辑寻址）</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="0" t="inlineStr">
         <is>
           <t>0x0F10</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="0" t="inlineStr">
         <is>
           <t>General Purpose Outputs</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="0" t="inlineStr">
         <is>
           <t>gpo[15:0]：通用输出（宽度 1/2/4/8 字节依 PDI）</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="0" t="inlineStr">
         <is>
           <t>0x0F18</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="0" t="inlineStr">
         <is>
           <t>General Purpose Inputs</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="0" t="inlineStr">
         <is>
           <t>gpi[15:0]：通用输入</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="0" t="inlineStr">
         <is>
           <t>User RAM / Process Data RAM</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
+      <c r="B127" s="0" t="inlineStr"/>
+      <c r="C127" s="0" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="0" t="inlineStr">
         <is>
           <t>0x0F80</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="0" t="inlineStr">
         <is>
           <t>User RAM</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="0" t="inlineStr">
         <is>
           <t>ram[127:0]：用户 RAM（128 字节）</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="0" t="inlineStr">
         <is>
           <t>0x1000</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="0" t="inlineStr">
         <is>
           <t>Process Data RAM</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="0" t="inlineStr">
         <is>
           <t>ram[7:0]（×8KB）：过程数据 RAM（ET1100=8KB；仅在 EEPROM 正确加载后 0x0110[0]=1 可访问）</t>
         </is>
